--- a/data/1st Round/Corrected/CdS3_2_Results Table.xlsx
+++ b/data/1st Round/Corrected/CdS3_2_Results Table.xlsx
@@ -2,23 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3804" yWindow="2340" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Corrected Results" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -49,12 +47,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -417,8 +416,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:T29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -511,6 +510,16 @@
           <t>Date</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Rseriescm2</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Rshuntcm2</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -551,9 +560,6 @@
       <c r="L2" t="n">
         <v>0.0005306</v>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
         <v>19.049</v>
       </c>
@@ -562,8 +568,14 @@
           <t>15:06:27</t>
         </is>
       </c>
-      <c r="R2" s="1" t="n">
-        <v>46267</v>
+      <c r="R2" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="S2" t="n">
+        <v>5.462649089169354</v>
+      </c>
+      <c r="T2" t="n">
+        <v>245.6066255368934</v>
       </c>
     </row>
     <row r="3">
@@ -605,9 +617,6 @@
       <c r="L3" t="n">
         <v>0.0005784400000000001</v>
       </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
         <v>19.05</v>
       </c>
@@ -616,8 +625,14 @@
           <t>15:09:05</t>
         </is>
       </c>
-      <c r="R3" s="1" t="n">
-        <v>46267</v>
+      <c r="R3" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5.618619839177491</v>
+      </c>
+      <c r="T3" t="n">
+        <v>243.1309164987352</v>
       </c>
     </row>
     <row r="4">
@@ -659,9 +674,6 @@
       <c r="L4" t="n">
         <v>0.0007514</v>
       </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
         <v>19.06</v>
       </c>
@@ -670,8 +682,14 @@
           <t>15:10:56</t>
         </is>
       </c>
-      <c r="R4" s="1" t="n">
-        <v>46267</v>
+      <c r="R4" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="S4" t="n">
+        <v>6.778294969595366</v>
+      </c>
+      <c r="T4" t="n">
+        <v>192.0803122103064</v>
       </c>
     </row>
     <row r="5">
@@ -713,9 +731,6 @@
       <c r="L5" t="n">
         <v>0.00081747</v>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
         <v>19.144</v>
       </c>
@@ -724,8 +739,14 @@
           <t>15:12:27</t>
         </is>
       </c>
-      <c r="R5" s="1" t="n">
-        <v>46267</v>
+      <c r="R5" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5.941586009115401</v>
+      </c>
+      <c r="T5" t="n">
+        <v>205.9252583926456</v>
       </c>
     </row>
     <row r="6">
@@ -767,9 +788,6 @@
       <c r="L6" t="n">
         <v>0.00066158</v>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
         <v>19.054</v>
       </c>
@@ -778,8 +796,14 @@
           <t>15:13:55</t>
         </is>
       </c>
-      <c r="R6" s="1" t="n">
-        <v>46267</v>
+      <c r="R6" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5.967090657367131</v>
+      </c>
+      <c r="T6" t="n">
+        <v>198.7523996414761</v>
       </c>
     </row>
     <row r="7">
@@ -821,9 +845,6 @@
       <c r="L7" t="n">
         <v>0.00073876</v>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
         <v>19.053</v>
       </c>
@@ -832,8 +853,14 @@
           <t>15:15:24</t>
         </is>
       </c>
-      <c r="R7" s="1" t="n">
-        <v>46267</v>
+      <c r="R7" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="S7" t="n">
+        <v>6.574395078435549</v>
+      </c>
+      <c r="T7" t="n">
+        <v>208.8445162350407</v>
       </c>
     </row>
     <row r="8">
@@ -875,9 +902,6 @@
       <c r="L8" t="n">
         <v>0.00091749</v>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
         <v>19.052</v>
       </c>
@@ -886,8 +910,14 @@
           <t>15:17:27</t>
         </is>
       </c>
-      <c r="R8" s="1" t="n">
-        <v>46267</v>
+      <c r="R8" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="S8" t="n">
+        <v>7.277190570165557</v>
+      </c>
+      <c r="T8" t="n">
+        <v>214.6225858661129</v>
       </c>
     </row>
     <row r="9">
@@ -929,9 +959,6 @@
       <c r="L9" t="n">
         <v>0.00090094</v>
       </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
         <v>19.063</v>
       </c>
@@ -940,8 +967,14 @@
           <t>15:19:11</t>
         </is>
       </c>
-      <c r="R9" s="1" t="n">
-        <v>46267</v>
+      <c r="R9" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="S9" t="n">
+        <v>6.598207066902458</v>
+      </c>
+      <c r="T9" t="n">
+        <v>225.3264973271462</v>
       </c>
     </row>
     <row r="10">
@@ -983,9 +1016,6 @@
       <c r="L10" t="n">
         <v>0.0006341</v>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
         <v>19.063</v>
       </c>
@@ -994,8 +1024,14 @@
           <t>15:20:59</t>
         </is>
       </c>
-      <c r="R10" s="1" t="n">
-        <v>46267</v>
+      <c r="R10" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="S10" t="n">
+        <v>6.06016399662628</v>
+      </c>
+      <c r="T10" t="n">
+        <v>207.1909198873831</v>
       </c>
     </row>
     <row r="11">
@@ -1037,9 +1073,6 @@
       <c r="L11" t="n">
         <v>0.00054851</v>
       </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
         <v>19.053</v>
       </c>
@@ -1048,8 +1081,14 @@
           <t>15:22:29</t>
         </is>
       </c>
-      <c r="R11" s="1" t="n">
-        <v>46267</v>
+      <c r="R11" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="S11" t="n">
+        <v>6.493681575677569</v>
+      </c>
+      <c r="T11" t="n">
+        <v>181.5203474139053</v>
       </c>
     </row>
     <row r="12">
@@ -1091,9 +1130,6 @@
       <c r="L12" t="n">
         <v>0.00073294</v>
       </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
         <v>19.049</v>
       </c>
@@ -1102,8 +1138,14 @@
           <t>15:24:01</t>
         </is>
       </c>
-      <c r="R12" s="1" t="n">
-        <v>46267</v>
+      <c r="R12" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="S12" t="n">
+        <v>7.414534795399703</v>
+      </c>
+      <c r="T12" t="n">
+        <v>77.79215463786439</v>
       </c>
     </row>
     <row r="13">
@@ -1145,9 +1187,6 @@
       <c r="L13" t="n">
         <v>0.00074674</v>
       </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
         <v>19.05</v>
       </c>
@@ -1156,8 +1195,14 @@
           <t>15:25:26</t>
         </is>
       </c>
-      <c r="R13" s="1" t="n">
-        <v>46267</v>
+      <c r="R13" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="S13" t="n">
+        <v>7.496246475072277</v>
+      </c>
+      <c r="T13" t="n">
+        <v>162.097225672059</v>
       </c>
     </row>
     <row r="14">
@@ -1199,9 +1244,6 @@
       <c r="L14" t="n">
         <v>0.00105768</v>
       </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
         <v>19.056</v>
       </c>
@@ -1210,8 +1252,14 @@
           <t>15:27:12</t>
         </is>
       </c>
-      <c r="R14" s="1" t="n">
-        <v>46267</v>
+      <c r="R14" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="S14" t="n">
+        <v>7.967657238337795</v>
+      </c>
+      <c r="T14" t="n">
+        <v>184.9480400100823</v>
       </c>
     </row>
     <row r="15">
@@ -1253,9 +1301,6 @@
       <c r="L15" t="n">
         <v>0.00113053</v>
       </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
         <v>19.063</v>
       </c>
@@ -1264,8 +1309,14 @@
           <t>15:32:45</t>
         </is>
       </c>
-      <c r="R15" s="1" t="n">
-        <v>46267</v>
+      <c r="R15" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="S15" t="n">
+        <v>8.361819866386151</v>
+      </c>
+      <c r="T15" t="n">
+        <v>190.4052100152174</v>
       </c>
     </row>
     <row r="16">
@@ -1307,9 +1358,6 @@
       <c r="L16" t="n">
         <v>0.0009136599999999999</v>
       </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
         <v>19.067</v>
       </c>
@@ -1318,8 +1366,14 @@
           <t>15:34:14</t>
         </is>
       </c>
-      <c r="R16" s="1" t="n">
-        <v>46267</v>
+      <c r="R16" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="S16" t="n">
+        <v>7.473298599083753</v>
+      </c>
+      <c r="T16" t="n">
+        <v>189.9306090619555</v>
       </c>
     </row>
     <row r="17">
@@ -1361,9 +1415,6 @@
       <c r="L17" t="n">
         <v>0.00065149</v>
       </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
         <v>19.145</v>
       </c>
@@ -1372,8 +1423,14 @@
           <t>15:35:55</t>
         </is>
       </c>
-      <c r="R17" s="1" t="n">
-        <v>46267</v>
+      <c r="R17" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="S17" t="n">
+        <v>6.501944115006689</v>
+      </c>
+      <c r="T17" t="n">
+        <v>172.1487806311529</v>
       </c>
     </row>
     <row r="18">
@@ -1415,9 +1472,6 @@
       <c r="L18" t="n">
         <v>0.00083273</v>
       </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
         <v>19.057</v>
       </c>
@@ -1426,8 +1480,14 @@
           <t>15:37:05</t>
         </is>
       </c>
-      <c r="R18" s="1" t="n">
-        <v>46267</v>
+      <c r="R18" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="S18" t="n">
+        <v>7.205911489900777</v>
+      </c>
+      <c r="T18" t="n">
+        <v>198.0174682408225</v>
       </c>
     </row>
     <row r="19">
@@ -1469,9 +1529,6 @@
       <c r="L19" t="n">
         <v>0.00083281</v>
       </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
         <v>19.064</v>
       </c>
@@ -1480,8 +1537,14 @@
           <t>15:38:38</t>
         </is>
       </c>
-      <c r="R19" s="1" t="n">
-        <v>46267</v>
+      <c r="R19" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="S19" t="n">
+        <v>6.426503438619326</v>
+      </c>
+      <c r="T19" t="n">
+        <v>246.3768926558003</v>
       </c>
     </row>
     <row r="20">
@@ -1523,9 +1586,6 @@
       <c r="L20" t="n">
         <v>0.00057305</v>
       </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
         <v>19.053</v>
       </c>
@@ -1534,8 +1594,14 @@
           <t>15:40:12</t>
         </is>
       </c>
-      <c r="R20" s="1" t="n">
-        <v>46267</v>
+      <c r="R20" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="S20" t="n">
+        <v>6.701114143460341</v>
+      </c>
+      <c r="T20" t="n">
+        <v>175.0206058959383</v>
       </c>
     </row>
     <row r="21">
@@ -1577,9 +1643,6 @@
       <c r="L21" t="n">
         <v>0.0006480499999999999</v>
       </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
         <v>19.062</v>
       </c>
@@ -1588,8 +1651,14 @@
           <t>15:41:10</t>
         </is>
       </c>
-      <c r="R21" s="1" t="n">
-        <v>46267</v>
+      <c r="R21" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5.618325168341999</v>
+      </c>
+      <c r="T21" t="n">
+        <v>67.09870600284002</v>
       </c>
     </row>
     <row r="22">
@@ -1631,9 +1700,6 @@
       <c r="L22" t="n">
         <v>0.00055277</v>
       </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
         <v>19.068</v>
       </c>
@@ -1642,8 +1708,14 @@
           <t>15:42:23</t>
         </is>
       </c>
-      <c r="R22" s="1" t="n">
-        <v>46267</v>
+      <c r="R22" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5.051321494797189</v>
+      </c>
+      <c r="T22" t="n">
+        <v>284.8391820244757</v>
       </c>
     </row>
     <row r="23">
@@ -1685,9 +1757,6 @@
       <c r="L23" t="n">
         <v>0.00052131</v>
       </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
         <v>19.082</v>
       </c>
@@ -1696,8 +1765,14 @@
           <t>15:43:24</t>
         </is>
       </c>
-      <c r="R23" s="1" t="n">
-        <v>46267</v>
+      <c r="R23" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="S23" t="n">
+        <v>6.039974860153584</v>
+      </c>
+      <c r="T23" t="n">
+        <v>194.6874090543764</v>
       </c>
     </row>
     <row r="24">
@@ -1739,9 +1814,6 @@
       <c r="L24" t="n">
         <v>0.00081992</v>
       </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
       <c r="P24" t="n">
         <v>19.063</v>
       </c>
@@ -1750,8 +1822,14 @@
           <t>15:44:46</t>
         </is>
       </c>
-      <c r="R24" s="1" t="n">
-        <v>46267</v>
+      <c r="R24" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5.706733969663293</v>
+      </c>
+      <c r="T24" t="n">
+        <v>229.2857209557593</v>
       </c>
     </row>
     <row r="25">
@@ -1793,9 +1871,6 @@
       <c r="L25" t="n">
         <v>0.00081981</v>
       </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
         <v>19.062</v>
       </c>
@@ -1804,8 +1879,14 @@
           <t>15:45:54</t>
         </is>
       </c>
-      <c r="R25" s="1" t="n">
-        <v>46267</v>
+      <c r="R25" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="S25" t="n">
+        <v>6.575015950751788</v>
+      </c>
+      <c r="T25" t="n">
+        <v>231.848824432004</v>
       </c>
     </row>
     <row r="26">
@@ -1847,9 +1928,6 @@
       <c r="L26" t="n">
         <v>0.00063796</v>
       </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
       <c r="P26" t="n">
         <v>19.064</v>
       </c>
@@ -1858,10 +1936,17 @@
           <t>15:47:28</t>
         </is>
       </c>
-      <c r="R26" s="1" t="n">
-        <v>46267</v>
-      </c>
-    </row>
+      <c r="R26" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5.538480977108591</v>
+      </c>
+      <c r="T26" t="n">
+        <v>280.9578742787603</v>
+      </c>
+    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
